--- a/data/outputs/apims_data_understanding.xlsx
+++ b/data/outputs/apims_data_understanding.xlsx
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C9" t="n">
         <v>55</v>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C13" t="n">
         <v>59</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C17" t="n">
         <v>60</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C24" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C26" t="n">
         <v>51</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C27" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C31" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C32" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C33" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C34" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C35" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C36" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C37" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C39" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C40" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C41" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C42" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C43" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C44" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C45" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C46" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C47" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C48" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C49" t="n">
         <v>31</v>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C50" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C51" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C53" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C55" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C56" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C57" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C58" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C59" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C60" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C61" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C62" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C63" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C64" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C66" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C67" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C68" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="C69" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
@@ -4008,22 +4008,22 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.37499999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>46141.58333333334</v>
+        <v>46149.375</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -4040,25 +4040,25 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>50.16176470588236</v>
+        <v>47.77941176470588</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>40.75</v>
+        <v>37</v>
       </c>
       <c r="I4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J4" t="n">
-        <v>59</v>
+        <v>56.25</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L4" t="n">
-        <v>10.25730215922303</v>
+        <v>15.02917122493839</v>
       </c>
     </row>
     <row r="5">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
